--- a/hira_material_automation/output/monthly/202601_202610__acl_primary_fixation_metal__040023__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202610__acl_primary_fixation_metal__040023__normalized.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-04T23:53:30</t>
+          <t>2026-10-14T23:47:03</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5f7cd73b0e4752a1dc31cd815db1c4d262a6acfa4dc9a3d0ec7e76aa28e5fb9e</t>
+          <t>82e98b36d48368851a171015972f05e5f6e12937cfc01e8464016f97a2cec305</t>
         </is>
       </c>
     </row>
